--- a/data/mic.xlsx
+++ b/data/mic.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MSU\codes\radiometer_processor\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B8AB86-E8D8-4AFA-8766-DD84C5DFE3FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9E88D5-2F0B-444E-8609-250D899ADEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C8199A0E-1241-4D75-8526-BBB4C7D6D381}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
